--- a/outputs/Riding_Tracker.xlsx
+++ b/outputs/Riding_Tracker.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Riding Tracker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Houses" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="House Blocks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Successions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Climate" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Relations" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Events" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Watch" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Handoff" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riding Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Houses" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="House Blocks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Successions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Climate" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relations" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watch" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handoff" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/Riding_Tracker.xlsx
+++ b/outputs/Riding_Tracker.xlsx
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-05 22:31:08</t>
+          <t>2026-10-06 19:19:54</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">

--- a/outputs/Riding_Tracker.xlsx
+++ b/outputs/Riding_Tracker.xlsx
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-06 19:19:54</t>
+          <t>2026-10-06 20:58:20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">

--- a/outputs/Riding_Tracker.xlsx
+++ b/outputs/Riding_Tracker.xlsx
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-06 20:58:20</t>
+          <t>2026-10-06 22:56:52</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
